--- a/Result/profitability/8042.xlsx
+++ b/Result/profitability/8042.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.55625</v>
       </c>
       <c r="N2" t="n">
-        <v>20.67625</v>
+        <v>20.64875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.97</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5900000000000001</v>
+        <v>0.6675</v>
       </c>
       <c r="N3" t="n">
-        <v>20.69125</v>
+        <v>20.765</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.52</v>
       </c>
       <c r="M4" t="n">
-        <v>0.645</v>
+        <v>0.7412500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>21.33625</v>
+        <v>21.415</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6900000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="N5" t="n">
-        <v>20.50625</v>
+        <v>20.9175</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.97</v>
       </c>
       <c r="M6" t="n">
-        <v>0.80875</v>
+        <v>0.85875</v>
       </c>
       <c r="N6" t="n">
-        <v>20.9625</v>
+        <v>21.1825</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.73</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9875</v>
+        <v>0.9937499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>22.38875</v>
+        <v>22.01</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1375</v>
+        <v>0.95375</v>
       </c>
       <c r="N8" t="n">
-        <v>22.0875</v>
+        <v>21.92</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8042</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1269</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1007</v>
+      </c>
+      <c r="E75" t="n">
+        <v>262</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="G75" t="n">
+        <v>102</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.07%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>109</v>
+      </c>
+      <c r="K75" t="n">
+        <v>92</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6774193548387097</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06099226217569409</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.289999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1897347174163784</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
